--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1102-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1102-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB5CED53-0810-4E85-8F8F-5E46C84E7EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1BD7B40-6100-4DEB-8DCC-1A5D827D6FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{0AF07108-9B5D-4231-B871-65CA570F6F3E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{78F11B95-7AF7-4355-B3C4-3522DEE712E9}"/>
   </bookViews>
   <sheets>
     <sheet name="1102-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1652,30 +1652,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDEF9C4-EA1D-498D-A7BD-75F79B55E014}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B146DB12-4F90-4CF0-9CD4-3C54EC58FE31}">
   <dimension ref="A1:X74"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1709,7 +1709,7 @@
       <c r="W1" s="33"/>
       <c r="X1" s="25"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1745,7 +1745,7 @@
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1865,7 +1865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>2025</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="42">
         <v>2024</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2023</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2022</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>6.02</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2021</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="42">
         <v>2020</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>8.66</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2019</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>8.52</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="42">
         <v>2018</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>8.35</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <v>2017</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="42">
         <v>2016</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>2015</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>2014</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>8.19</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>2013</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>2012</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>2011</v>
       </c>
@@ -4425,7 +4425,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>2010</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>2009</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>8.19</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="42">
         <v>2008</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="40">
         <v>2007</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>2006</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>7.71</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
         <v>2005</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="42">
         <v>2004</v>
       </c>
@@ -4929,7 +4929,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="40">
         <v>2003</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="42">
         <v>2002</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="40">
         <v>2001</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="42">
         <v>2000</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="40">
         <v>1999</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="42">
         <v>1998</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>7.94</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="40">
         <v>1997</v>
       </c>
@@ -5433,7 +5433,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="42">
         <v>1996</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="40">
         <v>1995</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="44">
         <v>1994</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="46"/>
       <c r="B57" s="47"/>
       <c r="C57" s="21" t="s">
@@ -5677,7 +5677,7 @@
       <c r="W57" s="53"/>
       <c r="X57" s="49"/>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="54">
         <v>1993</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="56"/>
       <c r="B59" s="57"/>
       <c r="C59" s="23" t="s">
@@ -5777,7 +5777,7 @@
       <c r="W59" s="63"/>
       <c r="X59" s="59"/>
     </row>
-    <row r="60" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="44">
         <v>1992</v>
       </c>
@@ -5849,7 +5849,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="46"/>
       <c r="B61" s="47"/>
       <c r="C61" s="21" t="s">
@@ -5877,7 +5877,7 @@
       <c r="W61" s="53"/>
       <c r="X61" s="49"/>
     </row>
-    <row r="62" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="54">
         <v>1991</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="56"/>
       <c r="B63" s="57"/>
       <c r="C63" s="23" t="s">
@@ -5977,7 +5977,7 @@
       <c r="W63" s="63"/>
       <c r="X63" s="59"/>
     </row>
-    <row r="64" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="44">
         <v>1990</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="46"/>
       <c r="B65" s="47"/>
       <c r="C65" s="21" t="s">
@@ -6077,7 +6077,7 @@
       <c r="W65" s="53"/>
       <c r="X65" s="49"/>
     </row>
-    <row r="66" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="54">
         <v>1989</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="56"/>
       <c r="B67" s="57"/>
       <c r="C67" s="23" t="s">
@@ -6177,7 +6177,7 @@
       <c r="W67" s="63"/>
       <c r="X67" s="59"/>
     </row>
-    <row r="68" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="42">
         <v>1988</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="40">
         <v>1987</v>
       </c>
@@ -6321,7 +6321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="42">
         <v>1986</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="40">
         <v>1985</v>
       </c>
@@ -6465,7 +6465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="42">
         <v>1984</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="40">
         <v>1983</v>
       </c>
@@ -6609,7 +6609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="42" t="s">
         <v>80</v>
       </c>
